--- a/Lead_Core_Pres_Üretim.xlsx
+++ b/Lead_Core_Pres_Üretim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Doğukan Kara\Desktop\Lead_Core\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E27B1A-5F61-4ABB-BECE-3E9D74E3772D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B51CE7B-E2D1-4E96-AA42-76C4B8B5009A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="8.08.2026" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,11 @@
     <sheet name="15.08.2026" sheetId="8" r:id="rId7"/>
     <sheet name="16.08.2026" sheetId="9" r:id="rId8"/>
     <sheet name="17.08.2026" sheetId="10" r:id="rId9"/>
+    <sheet name="18.08.2026" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'17.08.2026'!$A$1:$T$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'18.08.2026'!$A$1:$T$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="150">
   <si>
     <t>MAKİNE NO</t>
   </si>
@@ -414,6 +416,87 @@
   </si>
   <si>
     <t>MEHMET BOLAT</t>
+  </si>
+  <si>
+    <t>TARİH : 18.08.2026</t>
+  </si>
+  <si>
+    <t>MAKİNENİN TEL ÇEKME GÖVDESİ TORNAYA GİTTİ VARDİYA  SONU GELDİ.1 ADET LEAD CORE BASKI ZIMBASI VE BİR ADET MANDAL TUTUCU GÖVDE DEĞİŞTİ.</t>
+  </si>
+  <si>
+    <t>MAKİNE ARIZALIYDI 20 DK DURUŞ YAŞANDI.</t>
+  </si>
+  <si>
+    <t>32-27-33-17-70-56-58</t>
+  </si>
+  <si>
+    <t>31-69-71-55-15-53</t>
+  </si>
+  <si>
+    <t>23-28</t>
+  </si>
+  <si>
+    <t>30-73-6-54-48-52-60</t>
+  </si>
+  <si>
+    <t>35-75-95-16-51-88-49</t>
+  </si>
+  <si>
+    <t>8-38-33-27</t>
+  </si>
+  <si>
+    <t>18-55-48-41</t>
+  </si>
+  <si>
+    <t>83-94-64-57-18-26</t>
+  </si>
+  <si>
+    <t>86-81-61-87-68-21</t>
+  </si>
+  <si>
+    <t>59-29-82-16-19</t>
+  </si>
+  <si>
+    <t>MAKİNE ADET SAYMA SENSÖRÜ ARIZALIYDI, SONRADAN FARK EDİLDİ. ADET SAYISI EKSİK OLABİLİR.</t>
+  </si>
+  <si>
+    <t>8-85-63-65-24-67</t>
+  </si>
+  <si>
+    <t>47-84-62-74-66-50</t>
+  </si>
+  <si>
+    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE 16-15 TE KAPATILDI.</t>
+  </si>
+  <si>
+    <t>26-70-46-13-49-84-86-20</t>
+  </si>
+  <si>
+    <t>21-48-51-52-60-29-81-57</t>
+  </si>
+  <si>
+    <t>19-55-9-15-53-6-85-26</t>
+  </si>
+  <si>
+    <t>67-25-72-88-58-56-83-74</t>
+  </si>
+  <si>
+    <t>50-20-54-28-92-87-94</t>
+  </si>
+  <si>
+    <t>45-41-19</t>
+  </si>
+  <si>
+    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE 03:35 TE BAŞLADI.</t>
+  </si>
+  <si>
+    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE 02:40 DA ÇALIŞTILDI.</t>
+  </si>
+  <si>
+    <t>ARIZA VE DUURŞ BİLGİSİ BELİRTİLMEDİ.</t>
+  </si>
+  <si>
+    <t>34-54-56</t>
   </si>
 </sst>
 </file>
@@ -1242,6 +1325,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>249804</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>75206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>574482</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>128546</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Resim 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBDE5211-6717-4A89-ADFC-1329B9DCCC4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="249804" y="75206"/>
+          <a:ext cx="1749618" cy="434340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -3802,6 +3940,1957 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58648EDD-1F25-4911-9B42-94BC0677E445}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:T64"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" customWidth="1"/>
+    <col min="13" max="13" width="7.109375" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" customWidth="1"/>
+    <col min="15" max="15" width="7.44140625" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="12.88671875" customWidth="1"/>
+    <col min="18" max="20" width="20.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="89" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" s="90"/>
+    </row>
+    <row r="2" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="74"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="8">
+        <v>270000</v>
+      </c>
+      <c r="T3" s="6">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="95" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="96"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="R4" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="S4" s="67"/>
+      <c r="T4" s="68"/>
+    </row>
+    <row r="5" spans="1:20" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="92"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="62"/>
+      <c r="M5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="69">
+        <v>1</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="70">
+        <v>87094</v>
+      </c>
+      <c r="E6" s="70">
+        <v>89118</v>
+      </c>
+      <c r="F6" s="70">
+        <v>86110</v>
+      </c>
+      <c r="G6" s="46">
+        <f>SUM(D6:F6)</f>
+        <v>262322</v>
+      </c>
+      <c r="H6" s="46">
+        <f>SUM(G6:G10)</f>
+        <v>262322</v>
+      </c>
+      <c r="I6" s="46">
+        <v>455</v>
+      </c>
+      <c r="J6" s="46">
+        <v>459</v>
+      </c>
+      <c r="K6" s="46">
+        <v>454</v>
+      </c>
+      <c r="L6" s="46"/>
+      <c r="M6" s="60">
+        <f>(100*D6)/$T$3</f>
+        <v>96.771111111111111</v>
+      </c>
+      <c r="N6" s="60">
+        <f t="shared" ref="N6:O6" si="0">(100*E6)/$T$3</f>
+        <v>99.02</v>
+      </c>
+      <c r="O6" s="60">
+        <f t="shared" si="0"/>
+        <v>95.677777777777777</v>
+      </c>
+      <c r="P6" s="60">
+        <f>(H6*100)/$S$3</f>
+        <v>97.15629629629629</v>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="R6" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="S6" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="T6" s="39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="58"/>
+      <c r="B7" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="58"/>
+      <c r="B8" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="46">
+        <f t="shared" ref="G8" si="1">SUM(D8:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="58"/>
+      <c r="B9" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="58"/>
+      <c r="B10" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="46">
+        <f t="shared" ref="G10" si="2">SUM(D10:F10)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+    </row>
+    <row r="11" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="59"/>
+      <c r="B11" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="43"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="57">
+        <v>2</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="44">
+        <v>84604</v>
+      </c>
+      <c r="E12" s="44">
+        <v>88270</v>
+      </c>
+      <c r="F12" s="44">
+        <v>86964</v>
+      </c>
+      <c r="G12" s="46">
+        <f t="shared" ref="G12" si="3">SUM(D12:F12)</f>
+        <v>259838</v>
+      </c>
+      <c r="H12" s="42">
+        <f t="shared" ref="H12" si="4">SUM(G12:G16)</f>
+        <v>259838</v>
+      </c>
+      <c r="I12" s="42">
+        <v>451</v>
+      </c>
+      <c r="J12" s="42">
+        <v>460</v>
+      </c>
+      <c r="K12" s="42">
+        <v>464</v>
+      </c>
+      <c r="L12" s="42">
+        <v>12</v>
+      </c>
+      <c r="M12" s="32">
+        <f>(100*D12)/$T$3</f>
+        <v>94.004444444444445</v>
+      </c>
+      <c r="N12" s="32">
+        <f t="shared" ref="N12:O12" si="5">(100*E12)/$T$3</f>
+        <v>98.077777777777783</v>
+      </c>
+      <c r="O12" s="32">
+        <f t="shared" si="5"/>
+        <v>96.626666666666665</v>
+      </c>
+      <c r="P12" s="32">
+        <f>(H12*100)/$S$3</f>
+        <v>96.236296296296302</v>
+      </c>
+      <c r="Q12" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="S12" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="T12" s="39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="58"/>
+      <c r="B13" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+    </row>
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="46">
+        <f t="shared" ref="G14" si="6">SUM(D14:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="58"/>
+      <c r="B15" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+    </row>
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="58"/>
+      <c r="B16" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="46">
+        <f t="shared" ref="G16" si="7">SUM(D16:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+    </row>
+    <row r="17" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="59"/>
+      <c r="B17" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+    </row>
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="57">
+        <v>3</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="44">
+        <v>3102</v>
+      </c>
+      <c r="E18" s="44">
+        <v>70388</v>
+      </c>
+      <c r="F18" s="44">
+        <v>85774</v>
+      </c>
+      <c r="G18" s="46">
+        <f t="shared" ref="G18" si="8">SUM(D18:F18)</f>
+        <v>159264</v>
+      </c>
+      <c r="H18" s="42">
+        <f t="shared" ref="H18" si="9">SUM(G18:G22)</f>
+        <v>159264</v>
+      </c>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="32">
+        <f t="shared" ref="M18:O18" si="10">(100*D18)/$T$3</f>
+        <v>3.4466666666666668</v>
+      </c>
+      <c r="N18" s="32">
+        <f t="shared" si="10"/>
+        <v>78.208888888888893</v>
+      </c>
+      <c r="O18" s="32">
+        <f t="shared" si="10"/>
+        <v>95.304444444444442</v>
+      </c>
+      <c r="P18" s="32">
+        <f t="shared" ref="P18" si="11">(H18*100)/$S$3</f>
+        <v>58.986666666666665</v>
+      </c>
+      <c r="Q18" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="R18" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="S18" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="T18" s="39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="58"/>
+      <c r="B19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+    </row>
+    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="58"/>
+      <c r="B20" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="46">
+        <f t="shared" ref="G20" si="12">SUM(D20:F20)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="40"/>
+      <c r="S20" s="40"/>
+      <c r="T20" s="40"/>
+    </row>
+    <row r="21" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="58"/>
+      <c r="B21" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="58"/>
+      <c r="B22" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="46">
+        <f t="shared" ref="G22" si="13">SUM(D22:F22)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="59"/>
+      <c r="B23" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+    </row>
+    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="54">
+        <v>4</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="44">
+        <v>87573</v>
+      </c>
+      <c r="E24" s="44">
+        <v>90039</v>
+      </c>
+      <c r="F24" s="44">
+        <v>89647</v>
+      </c>
+      <c r="G24" s="46">
+        <f t="shared" ref="G24" si="14">SUM(D24:F24)</f>
+        <v>267259</v>
+      </c>
+      <c r="H24" s="43">
+        <f>SUM(G24:G28)</f>
+        <v>267259</v>
+      </c>
+      <c r="I24" s="53">
+        <v>453</v>
+      </c>
+      <c r="J24" s="53">
+        <v>455</v>
+      </c>
+      <c r="K24" s="53">
+        <v>464</v>
+      </c>
+      <c r="L24" s="53"/>
+      <c r="M24" s="34">
+        <f t="shared" ref="M24:O24" si="15">(100*D24)/$T$3</f>
+        <v>97.303333333333327</v>
+      </c>
+      <c r="N24" s="34">
+        <f t="shared" si="15"/>
+        <v>100.04333333333334</v>
+      </c>
+      <c r="O24" s="34">
+        <f t="shared" si="15"/>
+        <v>99.607777777777784</v>
+      </c>
+      <c r="P24" s="34">
+        <f t="shared" ref="P24" si="16">(H24*100)/$S$3</f>
+        <v>98.984814814814811</v>
+      </c>
+      <c r="Q24" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="R24" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="S24" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="T24" s="39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="54"/>
+      <c r="B25" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="40"/>
+    </row>
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="54"/>
+      <c r="B26" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="46">
+        <f t="shared" ref="G26" si="17">SUM(D26:F26)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="R26" s="40"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="40"/>
+    </row>
+    <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="54"/>
+      <c r="B27" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="43"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="40"/>
+    </row>
+    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="54"/>
+      <c r="B28" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="46">
+        <f t="shared" ref="G28" si="18">SUM(D28:F28)</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="R28" s="40"/>
+      <c r="S28" s="40"/>
+      <c r="T28" s="40"/>
+    </row>
+    <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="54"/>
+      <c r="B29" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="43"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+    </row>
+    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="54">
+        <v>5</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="46">
+        <f t="shared" ref="G30" si="19">SUM(D30:F30)</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="43">
+        <f>SUM(G30:G34)</f>
+        <v>274903</v>
+      </c>
+      <c r="I30" s="53">
+        <v>455</v>
+      </c>
+      <c r="J30" s="53">
+        <v>450</v>
+      </c>
+      <c r="K30" s="53">
+        <v>465</v>
+      </c>
+      <c r="L30" s="53"/>
+      <c r="M30" s="34">
+        <f t="shared" ref="M30:O30" si="20">(100*D30)/$T$3</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="34">
+        <f t="shared" ref="P30" si="21">(H30*100)/$S$3</f>
+        <v>101.81592592592592</v>
+      </c>
+      <c r="Q30" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="R30" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="S30" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="T30" s="39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="54"/>
+      <c r="B31" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="43"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="40"/>
+      <c r="T31" s="40"/>
+    </row>
+    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="54"/>
+      <c r="B32" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="46">
+        <f t="shared" ref="G32" si="22">SUM(D32:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="49"/>
+      <c r="P32" s="49"/>
+      <c r="Q32" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="R32" s="40"/>
+      <c r="S32" s="40"/>
+      <c r="T32" s="40"/>
+    </row>
+    <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="54"/>
+      <c r="B33" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="43"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="40"/>
+      <c r="T33" s="40"/>
+    </row>
+    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="54"/>
+      <c r="B34" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="44">
+        <v>90557</v>
+      </c>
+      <c r="E34" s="44">
+        <v>91710</v>
+      </c>
+      <c r="F34" s="44">
+        <v>92636</v>
+      </c>
+      <c r="G34" s="46">
+        <f t="shared" ref="G34" si="23">SUM(D34:F34)</f>
+        <v>274903</v>
+      </c>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="R34" s="40"/>
+      <c r="S34" s="40"/>
+      <c r="T34" s="40"/>
+    </row>
+    <row r="35" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="54"/>
+      <c r="B35" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="43"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+    </row>
+    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="54">
+        <v>6</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="44">
+        <v>81004</v>
+      </c>
+      <c r="E36" s="44">
+        <v>2426</v>
+      </c>
+      <c r="F36" s="44">
+        <v>46971</v>
+      </c>
+      <c r="G36" s="46">
+        <f t="shared" ref="G36" si="24">SUM(D36:F36)</f>
+        <v>130401</v>
+      </c>
+      <c r="H36" s="43">
+        <f>SUM(G36:G40)</f>
+        <v>130401</v>
+      </c>
+      <c r="I36" s="53">
+        <v>428</v>
+      </c>
+      <c r="J36" s="53">
+        <v>12</v>
+      </c>
+      <c r="K36" s="53">
+        <v>248</v>
+      </c>
+      <c r="L36" s="53"/>
+      <c r="M36" s="34">
+        <f t="shared" ref="M36:O36" si="25">(100*D36)/$T$3</f>
+        <v>90.004444444444445</v>
+      </c>
+      <c r="N36" s="34">
+        <f t="shared" si="25"/>
+        <v>2.6955555555555555</v>
+      </c>
+      <c r="O36" s="34">
+        <f t="shared" si="25"/>
+        <v>52.19</v>
+      </c>
+      <c r="P36" s="34">
+        <f t="shared" ref="P36" si="26">(H36*100)/$S$3</f>
+        <v>48.296666666666667</v>
+      </c>
+      <c r="Q36" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="R36" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="S36" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="T36" s="39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="54"/>
+      <c r="B37" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="43"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="40"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="40"/>
+    </row>
+    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="54"/>
+      <c r="B38" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="42"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="46">
+        <f t="shared" ref="G38" si="27">SUM(D38:F38)</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="43"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="34"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="34"/>
+      <c r="P38" s="34"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="40"/>
+      <c r="S38" s="50"/>
+      <c r="T38" s="40"/>
+    </row>
+    <row r="39" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="54"/>
+      <c r="B39" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="43"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="49"/>
+      <c r="N39" s="49"/>
+      <c r="O39" s="49"/>
+      <c r="P39" s="49"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="40"/>
+      <c r="S39" s="51"/>
+      <c r="T39" s="40"/>
+    </row>
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="54"/>
+      <c r="B40" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="42"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="46">
+        <f t="shared" ref="G40" si="28">SUM(D40:F40)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="49"/>
+      <c r="N40" s="49"/>
+      <c r="O40" s="49"/>
+      <c r="P40" s="49"/>
+      <c r="Q40" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="R40" s="40"/>
+      <c r="S40" s="51"/>
+      <c r="T40" s="40"/>
+    </row>
+    <row r="41" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="54"/>
+      <c r="B41" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="43"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
+      <c r="P41" s="49"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="41"/>
+      <c r="S41" s="51"/>
+      <c r="T41" s="41"/>
+    </row>
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="54">
+        <v>7</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="44">
+        <v>84140</v>
+      </c>
+      <c r="E42" s="44">
+        <v>3833</v>
+      </c>
+      <c r="F42" s="44">
+        <v>56023</v>
+      </c>
+      <c r="G42" s="46">
+        <f t="shared" ref="G42" si="29">SUM(D42:F42)</f>
+        <v>143996</v>
+      </c>
+      <c r="H42" s="43">
+        <f>SUM(G42:G46)</f>
+        <v>143996</v>
+      </c>
+      <c r="I42" s="53">
+        <v>455</v>
+      </c>
+      <c r="J42" s="53">
+        <v>15</v>
+      </c>
+      <c r="K42" s="53">
+        <v>303</v>
+      </c>
+      <c r="L42" s="53"/>
+      <c r="M42" s="34">
+        <f t="shared" ref="M42:O42" si="30">(100*D42)/$T$3</f>
+        <v>93.488888888888894</v>
+      </c>
+      <c r="N42" s="34">
+        <f t="shared" si="30"/>
+        <v>4.2588888888888885</v>
+      </c>
+      <c r="O42" s="34">
+        <f t="shared" si="30"/>
+        <v>62.247777777777777</v>
+      </c>
+      <c r="P42" s="34">
+        <f>(H42*100)/$S$3</f>
+        <v>53.331851851851852</v>
+      </c>
+      <c r="Q42" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="R42" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="S42" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="T42" s="39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="54"/>
+      <c r="B43" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="43"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="40"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="40"/>
+    </row>
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="54"/>
+      <c r="B44" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="42"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="46">
+        <f t="shared" ref="G44" si="31">SUM(D44:F44)</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="49"/>
+      <c r="P44" s="49"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="40"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="40"/>
+    </row>
+    <row r="45" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="54"/>
+      <c r="B45" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="43"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="49"/>
+      <c r="N45" s="49"/>
+      <c r="O45" s="49"/>
+      <c r="P45" s="49"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="40"/>
+      <c r="S45" s="51"/>
+      <c r="T45" s="40"/>
+    </row>
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="54"/>
+      <c r="B46" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C46" s="42"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="46">
+        <f t="shared" ref="G46" si="32">SUM(D46:F46)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="42"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="49"/>
+      <c r="N46" s="49"/>
+      <c r="O46" s="49"/>
+      <c r="P46" s="49"/>
+      <c r="Q46" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="R46" s="40"/>
+      <c r="S46" s="51"/>
+      <c r="T46" s="40"/>
+    </row>
+    <row r="47" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="54"/>
+      <c r="B47" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="49"/>
+      <c r="N47" s="49"/>
+      <c r="O47" s="49"/>
+      <c r="P47" s="49"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="51"/>
+      <c r="T47" s="41"/>
+    </row>
+    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C48" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="37">
+        <f>SUM(D6:D47)</f>
+        <v>518074</v>
+      </c>
+      <c r="E48" s="37">
+        <f>SUM(E6:E47)</f>
+        <v>435784</v>
+      </c>
+      <c r="F48" s="37">
+        <f>SUM(F6:F47)</f>
+        <v>544125</v>
+      </c>
+      <c r="G48" s="37">
+        <f>SUM(G6:G46)</f>
+        <v>1497983</v>
+      </c>
+      <c r="H48" s="37">
+        <f>SUM(H6:H47)</f>
+        <v>1497983</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="36"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="J49" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="L49" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="M49" s="28"/>
+      <c r="N49" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="O49" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="P49" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q49" s="22"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="J50" s="19">
+        <v>3</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="L50" s="29">
+        <v>6</v>
+      </c>
+      <c r="M50" s="30"/>
+      <c r="N50" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="O50" s="19">
+        <v>6</v>
+      </c>
+      <c r="P50" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q50" s="23"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="29">
+        <v>7</v>
+      </c>
+      <c r="M51" s="30"/>
+      <c r="N51" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="O51" s="19">
+        <v>7</v>
+      </c>
+      <c r="P51" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q51" s="23"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="24"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="J53" s="19"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="19"/>
+      <c r="O53" s="19"/>
+      <c r="P53" s="19"/>
+      <c r="Q53" s="24"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="Q54" s="25"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="I64" t="s">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s">
+        <v>108</v>
+      </c>
+      <c r="K64" t="s">
+        <v>109</v>
+      </c>
+      <c r="M64" t="s">
+        <v>65</v>
+      </c>
+      <c r="O64" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="242">
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="T42:T47"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="Q44:Q45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="N42:N47"/>
+    <mergeCell ref="O42:O47"/>
+    <mergeCell ref="P42:P47"/>
+    <mergeCell ref="Q42:Q43"/>
+    <mergeCell ref="R42:R47"/>
+    <mergeCell ref="S42:S47"/>
+    <mergeCell ref="Q46:Q47"/>
+    <mergeCell ref="H42:H47"/>
+    <mergeCell ref="I42:I47"/>
+    <mergeCell ref="J42:J47"/>
+    <mergeCell ref="K42:K47"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="M42:M47"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="T36:T41"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="N36:N41"/>
+    <mergeCell ref="O36:O41"/>
+    <mergeCell ref="P36:P41"/>
+    <mergeCell ref="Q36:Q37"/>
+    <mergeCell ref="R36:R41"/>
+    <mergeCell ref="S36:S41"/>
+    <mergeCell ref="Q40:Q41"/>
+    <mergeCell ref="H36:H41"/>
+    <mergeCell ref="I36:I41"/>
+    <mergeCell ref="J36:J41"/>
+    <mergeCell ref="K36:K41"/>
+    <mergeCell ref="L36:L41"/>
+    <mergeCell ref="M36:M41"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="T30:T35"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="Q32:Q33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="N30:N35"/>
+    <mergeCell ref="O30:O35"/>
+    <mergeCell ref="P30:P35"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="R30:R35"/>
+    <mergeCell ref="S30:S35"/>
+    <mergeCell ref="Q34:Q35"/>
+    <mergeCell ref="H30:H35"/>
+    <mergeCell ref="I30:I35"/>
+    <mergeCell ref="J30:J35"/>
+    <mergeCell ref="K30:K35"/>
+    <mergeCell ref="L30:L35"/>
+    <mergeCell ref="M30:M35"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="T24:T29"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="N24:N29"/>
+    <mergeCell ref="O24:O29"/>
+    <mergeCell ref="P24:P29"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="R24:R29"/>
+    <mergeCell ref="S24:S29"/>
+    <mergeCell ref="Q28:Q29"/>
+    <mergeCell ref="H24:H29"/>
+    <mergeCell ref="I24:I29"/>
+    <mergeCell ref="J24:J29"/>
+    <mergeCell ref="K24:K29"/>
+    <mergeCell ref="L24:L29"/>
+    <mergeCell ref="M24:M29"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="T18:T23"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="N18:N23"/>
+    <mergeCell ref="O18:O23"/>
+    <mergeCell ref="P18:P23"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="R18:R23"/>
+    <mergeCell ref="S18:S23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="H18:H23"/>
+    <mergeCell ref="I18:I23"/>
+    <mergeCell ref="J18:J23"/>
+    <mergeCell ref="K18:K23"/>
+    <mergeCell ref="L18:L23"/>
+    <mergeCell ref="M18:M23"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="O12:O17"/>
+    <mergeCell ref="P12:P17"/>
+    <mergeCell ref="Q12:Q13"/>
+    <mergeCell ref="R12:R17"/>
+    <mergeCell ref="S12:S17"/>
+    <mergeCell ref="T12:T17"/>
+    <mergeCell ref="I12:I17"/>
+    <mergeCell ref="J12:J17"/>
+    <mergeCell ref="K12:K17"/>
+    <mergeCell ref="L12:L17"/>
+    <mergeCell ref="M12:M17"/>
+    <mergeCell ref="N12:N17"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H17"/>
+    <mergeCell ref="T6:T11"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="N6:N11"/>
+    <mergeCell ref="O6:O11"/>
+    <mergeCell ref="P6:P11"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R11"/>
+    <mergeCell ref="S6:S11"/>
+    <mergeCell ref="H6:H11"/>
+    <mergeCell ref="I6:I11"/>
+    <mergeCell ref="J6:J11"/>
+    <mergeCell ref="K6:K11"/>
+    <mergeCell ref="L6:L11"/>
+    <mergeCell ref="M6:M11"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:R3"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:K4"/>
+  </mergeCells>
+  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="8" scale="94" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1D6850-0181-485E-8D4B-F7E3A66DA37D}">
   <sheetPr>

--- a/Lead_Core_Pres_Üretim.xlsx
+++ b/Lead_Core_Pres_Üretim.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Doğukan Kara\Desktop\Lead_Core\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Doğukan Kara\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AD4986-13B6-4277-8630-E842338E7C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037B9452-A97B-4425-A8C2-B80E03774CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,9 @@
     <sheet name="15.08.2026" sheetId="8" r:id="rId6"/>
     <sheet name="16.08.2026" sheetId="9" r:id="rId7"/>
     <sheet name="17.08.2026" sheetId="10" r:id="rId8"/>
-    <sheet name="18.08.2026" sheetId="11" r:id="rId9"/>
-    <sheet name="19.08.2026" sheetId="12" r:id="rId10"/>
-    <sheet name="20.08.2026" sheetId="13" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'17.08.2026'!$A$1:$T$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'18.08.2026'!$A$1:$T$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'19.08.2026'!$A$1:$T$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'20.08.2026'!$A$1:$T$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="118">
   <si>
     <t>MAKİNE NO</t>
   </si>
@@ -404,240 +398,6 @@
   </si>
   <si>
     <t>MEHMET BOLAT</t>
-  </si>
-  <si>
-    <t>TARİH : 18.08.2026</t>
-  </si>
-  <si>
-    <t>MAKİNENİN TEL ÇEKME GÖVDESİ TORNAYA GİTTİ VARDİYA  SONU GELDİ.1 ADET LEAD CORE BASKI ZIMBASI VE BİR ADET MANDAL TUTUCU GÖVDE DEĞİŞTİ.</t>
-  </si>
-  <si>
-    <t>MAKİNE ARIZALIYDI 20 DK DURUŞ YAŞANDI.</t>
-  </si>
-  <si>
-    <t>32-27-33-17-70-56-58</t>
-  </si>
-  <si>
-    <t>31-69-71-55-15-53</t>
-  </si>
-  <si>
-    <t>23-28</t>
-  </si>
-  <si>
-    <t>30-73-6-54-48-52-60</t>
-  </si>
-  <si>
-    <t>35-75-95-16-51-88-49</t>
-  </si>
-  <si>
-    <t>8-38-33-27</t>
-  </si>
-  <si>
-    <t>18-55-48-41</t>
-  </si>
-  <si>
-    <t>83-94-64-57-18-26</t>
-  </si>
-  <si>
-    <t>86-81-61-87-68-21</t>
-  </si>
-  <si>
-    <t>59-29-82-16-19</t>
-  </si>
-  <si>
-    <t>MAKİNE ADET SAYMA SENSÖRÜ ARIZALIYDI, SONRADAN FARK EDİLDİ. ADET SAYISI EKSİK OLABİLİR.</t>
-  </si>
-  <si>
-    <t>8-85-63-65-24-67</t>
-  </si>
-  <si>
-    <t>47-84-62-74-66-50</t>
-  </si>
-  <si>
-    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE 16-15 TE KAPATILDI.</t>
-  </si>
-  <si>
-    <t>26-70-46-13-49-84-86-20</t>
-  </si>
-  <si>
-    <t>21-48-51-52-60-29-81-57</t>
-  </si>
-  <si>
-    <t>19-55-9-15-53-6-85-26</t>
-  </si>
-  <si>
-    <t>67-25-72-88-58-56-83-74</t>
-  </si>
-  <si>
-    <t>50-20-54-28-92-87-94</t>
-  </si>
-  <si>
-    <t>45-41-19</t>
-  </si>
-  <si>
-    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE 03:35 TE BAŞLADI.</t>
-  </si>
-  <si>
-    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE 02:40 DA ÇALIŞTILDI.</t>
-  </si>
-  <si>
-    <t>ARIZA VE DUURŞ BİLGİSİ BELİRTİLMEDİ.</t>
-  </si>
-  <si>
-    <t>34-54-56</t>
-  </si>
-  <si>
-    <t>TARİH : 19.08.2026</t>
-  </si>
-  <si>
-    <t>KARE MİL, ÇENE, ÇENE PİMİ,VE 1 ADET LEAD CORE BASKI ZIMBASI DEĞİŞTİ.</t>
-  </si>
-  <si>
-    <t>1 ADET BASKI ZIMBASI DEĞİŞTİ, MAKİNE ARIZALANDI GİDERİLEMEDİ. DİĞER VARDİYAYA TESLİM EDİLDİ.</t>
-  </si>
-  <si>
-    <t>MAKİNE ARIZALI TESLİM ALINDI, 2 ADET LEAD CORE BASKI ZIMBASI DEĞİŞTİ. TAŞIYIICI AYARI, MANDAL AYARI VE ZAMAN AYARI YAPILDI.ÇENE VE MANDAL GÖVDESİ DEĞİŞTİ.</t>
-  </si>
-  <si>
-    <t>1 ADET LEAD CORE BASKI ZIMBASI DEĞİŞTİ</t>
-  </si>
-  <si>
-    <t>30-7-9-50</t>
-  </si>
-  <si>
-    <t>66-51-83-55-81-58</t>
-  </si>
-  <si>
-    <t>69-64-74-24-28-60-</t>
-  </si>
-  <si>
-    <t>32-57-54-15-72-85-92</t>
-  </si>
-  <si>
-    <t>27-8-16-67-25-6-30</t>
-  </si>
-  <si>
-    <t>73-20-26-13-9-88</t>
-  </si>
-  <si>
-    <t>22-39-26-34</t>
-  </si>
-  <si>
-    <t>88-86-17-77</t>
-  </si>
-  <si>
-    <t>60-85-52-36-34-95</t>
-  </si>
-  <si>
-    <t>6-28-29-18-23-47</t>
-  </si>
-  <si>
-    <t>58-80-31-22-10-75</t>
-  </si>
-  <si>
-    <t>92-46-53-78-30-71</t>
-  </si>
-  <si>
-    <t>46-24-6-5</t>
-  </si>
-  <si>
-    <t>46-8-33-35</t>
-  </si>
-  <si>
-    <t>61-12-54-66-70-15</t>
-  </si>
-  <si>
-    <t>47-62-50-24-72-55</t>
-  </si>
-  <si>
-    <t>82-64-48</t>
-  </si>
-  <si>
-    <t>65-67-16-51-9-13</t>
-  </si>
-  <si>
-    <t>8-59-21-18-25-89</t>
-  </si>
-  <si>
-    <t>45-15-18</t>
-  </si>
-  <si>
-    <t>10-38-34-1-7</t>
-  </si>
-  <si>
-    <t>TARİH : 20.08.2026</t>
-  </si>
-  <si>
-    <t>23-46-76-20-64-87</t>
-  </si>
-  <si>
-    <t>36-33-48-74-27-24</t>
-  </si>
-  <si>
-    <t>78-71-77-69-83</t>
-  </si>
-  <si>
-    <t>MAKİNE 09:19 DA 6,20 - 6,25 ÇALIŞMAYA BAŞLADI</t>
-  </si>
-  <si>
-    <t>34-95-10-57-15-16</t>
-  </si>
-  <si>
-    <t>17-86-75-8-55-13</t>
-  </si>
-  <si>
-    <t>31-39-15</t>
-  </si>
-  <si>
-    <t>22-43-48-38</t>
-  </si>
-  <si>
-    <t>51-92-67-46-10-76</t>
-  </si>
-  <si>
-    <t>PENS YATAĞI KIRILDI. PENS YATAĞI, PENS KAPAĞI VE LEAD CORE BASKI ZIMBASI DEĞİŞTİ.</t>
-  </si>
-  <si>
-    <t>30-28-86-78-20-71</t>
-  </si>
-  <si>
-    <t>73-85-36-21-48</t>
-  </si>
-  <si>
-    <t>1 ADET BASKI ZIMBASI DEĞİŞTİ. ZAMANLAYICI AYARI YAPILDI.</t>
-  </si>
-  <si>
-    <t>6-38-3-47-77-74</t>
-  </si>
-  <si>
-    <t>54-60-34-75-55</t>
-  </si>
-  <si>
-    <t>4 MM TEL OLMADIĞINDAN MAKİNE 18:25 TE KAPATILDI.</t>
-  </si>
-  <si>
-    <t>4 MM TEL OLMADIĞINDAN MAKİNE 18:00 DA KAPATILDI.</t>
-  </si>
-  <si>
-    <t>51-24-6-34-36-73</t>
-  </si>
-  <si>
-    <t>TEL AZLIĞINDNA DOLAYI MAKİNE MOLALARDA DURDURULDU.</t>
-  </si>
-  <si>
-    <t>95-16-83-15-31-33</t>
-  </si>
-  <si>
-    <t>69-35-87-60-28-25</t>
-  </si>
-  <si>
-    <t>64-13-86-92-77-66</t>
-  </si>
-  <si>
-    <t>27-57-46-54-53-67</t>
-  </si>
-  <si>
-    <t>TEL OLMADIĞINDAN DOLAYI MAKİNE ÇALIŞMADI.</t>
   </si>
 </sst>
 </file>
@@ -1454,116 +1214,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>249804</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>75206</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>574482</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>128546</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Resim 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{217A0653-B2CE-454D-99D0-B733A8456381}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="249804" y="75206"/>
-          <a:ext cx="1749618" cy="434340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>249804</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>75206</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>574482</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>128546</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Resim 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F0618AD-5577-4104-8B44-18E91B9FF35B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="249804" y="75206"/>
-          <a:ext cx="1749618" cy="434340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1949,61 +1599,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>249804</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>75206</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>574482</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>128546</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Resim 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBDE5211-6717-4A89-ADFC-1329B9DCCC4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="249804" y="75206"/>
-          <a:ext cx="1749618" cy="434340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4071,3880 +3666,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2642463A-E6D6-48FF-B042-7D8F9077AEDF}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:T64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="12" max="12" width="5.33203125" customWidth="1"/>
-    <col min="13" max="13" width="7.109375" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="15" width="7.44140625" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" customWidth="1"/>
-    <col min="18" max="20" width="20.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="68"/>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="86" t="s">
-        <v>145</v>
-      </c>
-      <c r="T1" s="87"/>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="8">
-        <v>270000</v>
-      </c>
-      <c r="T3" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="90" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="92" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="93"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="R4" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="64"/>
-      <c r="T4" s="65"/>
-    </row>
-    <row r="5" spans="1:20" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="89"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="66">
-        <v>1</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="67">
-        <v>85414</v>
-      </c>
-      <c r="E6" s="67">
-        <v>84383</v>
-      </c>
-      <c r="F6" s="67">
-        <v>86405</v>
-      </c>
-      <c r="G6" s="40">
-        <f>SUM(D6:F6)</f>
-        <v>256202</v>
-      </c>
-      <c r="H6" s="40">
-        <f>SUM(G6:G10)</f>
-        <v>256202</v>
-      </c>
-      <c r="I6" s="40">
-        <v>450</v>
-      </c>
-      <c r="J6" s="40">
-        <v>445</v>
-      </c>
-      <c r="K6" s="40">
-        <v>456</v>
-      </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="57">
-        <f>(100*D6)/$T$3</f>
-        <v>94.904444444444451</v>
-      </c>
-      <c r="N6" s="57">
-        <f t="shared" ref="N6:O6" si="0">(100*E6)/$T$3</f>
-        <v>93.75888888888889</v>
-      </c>
-      <c r="O6" s="57">
-        <f t="shared" si="0"/>
-        <v>96.00555555555556</v>
-      </c>
-      <c r="P6" s="57">
-        <f>(H6*100)/$S$3</f>
-        <v>94.889629629629624</v>
-      </c>
-      <c r="Q6" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="R6" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="T6" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="55"/>
-      <c r="B7" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55"/>
-      <c r="B8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="40">
-        <f t="shared" ref="G8" si="1">SUM(D8:F8)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="52"/>
-      <c r="Q8" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="55"/>
-      <c r="B9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55"/>
-      <c r="B10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="40">
-        <f t="shared" ref="G10" si="2">SUM(D10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-    </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
-      <c r="B11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <v>2</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="38">
-        <v>83004</v>
-      </c>
-      <c r="E12" s="38">
-        <v>83481</v>
-      </c>
-      <c r="F12" s="38">
-        <v>85451</v>
-      </c>
-      <c r="G12" s="40">
-        <f t="shared" ref="G12" si="3">SUM(D12:F12)</f>
-        <v>251936</v>
-      </c>
-      <c r="H12" s="36">
-        <f t="shared" ref="H12" si="4">SUM(G12:G16)</f>
-        <v>251936</v>
-      </c>
-      <c r="I12" s="36">
-        <v>443</v>
-      </c>
-      <c r="J12" s="36">
-        <v>446</v>
-      </c>
-      <c r="K12" s="36">
-        <v>456</v>
-      </c>
-      <c r="L12" s="36">
-        <v>12</v>
-      </c>
-      <c r="M12" s="51">
-        <f>(100*D12)/$T$3</f>
-        <v>92.226666666666674</v>
-      </c>
-      <c r="N12" s="51">
-        <f t="shared" ref="N12:O12" si="5">(100*E12)/$T$3</f>
-        <v>92.756666666666661</v>
-      </c>
-      <c r="O12" s="51">
-        <f t="shared" si="5"/>
-        <v>94.945555555555558</v>
-      </c>
-      <c r="P12" s="51">
-        <f>(H12*100)/$S$3</f>
-        <v>93.309629629629626</v>
-      </c>
-      <c r="Q12" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R12" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S12" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T12" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="55"/>
-      <c r="B13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55"/>
-      <c r="B14" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="40">
-        <f t="shared" ref="G14" si="6">SUM(D14:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="55"/>
-      <c r="B15" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="40">
-        <f t="shared" ref="G16" si="7">SUM(D16:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-    </row>
-    <row r="17" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
-      <c r="B17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-    </row>
-    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <v>3</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="38">
-        <v>34707</v>
-      </c>
-      <c r="E18" s="38">
-        <v>85541</v>
-      </c>
-      <c r="F18" s="38">
-        <v>79543</v>
-      </c>
-      <c r="G18" s="40">
-        <f t="shared" ref="G18" si="8">SUM(D18:F18)</f>
-        <v>199791</v>
-      </c>
-      <c r="H18" s="36">
-        <f t="shared" ref="H18" si="9">SUM(G18:G22)</f>
-        <v>199791</v>
-      </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="51">
-        <f t="shared" ref="M18:O18" si="10">(100*D18)/$T$3</f>
-        <v>38.563333333333333</v>
-      </c>
-      <c r="N18" s="51">
-        <f t="shared" si="10"/>
-        <v>95.045555555555552</v>
-      </c>
-      <c r="O18" s="51">
-        <f t="shared" si="10"/>
-        <v>88.38111111111111</v>
-      </c>
-      <c r="P18" s="51">
-        <f t="shared" ref="P18" si="11">(H18*100)/$S$3</f>
-        <v>73.99666666666667</v>
-      </c>
-      <c r="Q18" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="R18" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="S18" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="55"/>
-      <c r="B19" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-    </row>
-    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="40">
-        <f t="shared" ref="G20" si="12">SUM(D20:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-    </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="55"/>
-      <c r="B21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-    </row>
-    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="55"/>
-      <c r="B22" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="40">
-        <f t="shared" ref="G22" si="13">SUM(D22:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-    </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
-      <c r="B23" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-    </row>
-    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50">
-        <v>4</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="38">
-        <v>86799</v>
-      </c>
-      <c r="E24" s="38">
-        <v>87064</v>
-      </c>
-      <c r="F24" s="38">
-        <v>85019</v>
-      </c>
-      <c r="G24" s="40">
-        <f t="shared" ref="G24" si="14">SUM(D24:F24)</f>
-        <v>258882</v>
-      </c>
-      <c r="H24" s="37">
-        <f>SUM(G24:G28)</f>
-        <v>258882</v>
-      </c>
-      <c r="I24" s="49">
-        <v>449</v>
-      </c>
-      <c r="J24" s="49">
-        <v>451</v>
-      </c>
-      <c r="K24" s="49">
-        <v>441</v>
-      </c>
-      <c r="L24" s="49"/>
-      <c r="M24" s="44">
-        <f t="shared" ref="M24:O24" si="15">(100*D24)/$T$3</f>
-        <v>96.443333333333328</v>
-      </c>
-      <c r="N24" s="44">
-        <f t="shared" si="15"/>
-        <v>96.737777777777779</v>
-      </c>
-      <c r="O24" s="44">
-        <f t="shared" si="15"/>
-        <v>94.465555555555554</v>
-      </c>
-      <c r="P24" s="44">
-        <f t="shared" ref="P24" si="16">(H24*100)/$S$3</f>
-        <v>95.882222222222225</v>
-      </c>
-      <c r="Q24" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="R24" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S24" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T24" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="50"/>
-      <c r="B25" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-    </row>
-    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50"/>
-      <c r="B26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="40">
-        <f t="shared" ref="G26" si="17">SUM(D26:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-    </row>
-    <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="50"/>
-      <c r="B27" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-    </row>
-    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="50"/>
-      <c r="B28" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="40">
-        <f t="shared" ref="G28" si="18">SUM(D28:F28)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-    </row>
-    <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="50"/>
-      <c r="B29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-    </row>
-    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="50">
-        <v>5</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="38">
-        <v>89808</v>
-      </c>
-      <c r="E30" s="38">
-        <v>90337</v>
-      </c>
-      <c r="F30" s="38">
-        <v>86017</v>
-      </c>
-      <c r="G30" s="40">
-        <f t="shared" ref="G30" si="19">SUM(D30:F30)</f>
-        <v>266162</v>
-      </c>
-      <c r="H30" s="37">
-        <f>SUM(G30:G34)</f>
-        <v>266162</v>
-      </c>
-      <c r="I30" s="49">
-        <v>451</v>
-      </c>
-      <c r="J30" s="49">
-        <v>453</v>
-      </c>
-      <c r="K30" s="49">
-        <v>432</v>
-      </c>
-      <c r="L30" s="49"/>
-      <c r="M30" s="44">
-        <f t="shared" ref="M30:O30" si="20">(100*D30)/$T$3</f>
-        <v>99.786666666666662</v>
-      </c>
-      <c r="N30" s="44">
-        <f t="shared" si="20"/>
-        <v>100.37444444444445</v>
-      </c>
-      <c r="O30" s="44">
-        <f t="shared" si="20"/>
-        <v>95.574444444444438</v>
-      </c>
-      <c r="P30" s="44">
-        <f t="shared" ref="P30" si="21">(H30*100)/$S$3</f>
-        <v>98.578518518518521</v>
-      </c>
-      <c r="Q30" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="R30" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S30" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T30" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="50"/>
-      <c r="B31" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-    </row>
-    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="40">
-        <f t="shared" ref="G32" si="22">SUM(D32:F32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-    </row>
-    <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="50"/>
-      <c r="B33" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-    </row>
-    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="50"/>
-      <c r="B34" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="40">
-        <f t="shared" ref="G34" si="23">SUM(D34:F34)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-    </row>
-    <row r="35" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="50"/>
-      <c r="B35" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-    </row>
-    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="50">
-        <v>6</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="38">
-        <v>68554</v>
-      </c>
-      <c r="E36" s="38">
-        <v>67238</v>
-      </c>
-      <c r="F36" s="38">
-        <v>74280</v>
-      </c>
-      <c r="G36" s="40">
-        <f t="shared" ref="G36" si="24">SUM(D36:F36)</f>
-        <v>210072</v>
-      </c>
-      <c r="H36" s="37">
-        <f>SUM(G36:G40)</f>
-        <v>210072</v>
-      </c>
-      <c r="I36" s="49">
-        <v>359</v>
-      </c>
-      <c r="J36" s="49">
-        <v>380</v>
-      </c>
-      <c r="K36" s="49">
-        <v>427</v>
-      </c>
-      <c r="L36" s="49"/>
-      <c r="M36" s="44">
-        <f t="shared" ref="M36:O36" si="25">(100*D36)/$T$3</f>
-        <v>76.171111111111117</v>
-      </c>
-      <c r="N36" s="44">
-        <f t="shared" si="25"/>
-        <v>74.708888888888893</v>
-      </c>
-      <c r="O36" s="44">
-        <f t="shared" si="25"/>
-        <v>82.533333333333331</v>
-      </c>
-      <c r="P36" s="44">
-        <f t="shared" ref="P36" si="26">(H36*100)/$S$3</f>
-        <v>77.804444444444442</v>
-      </c>
-      <c r="Q36" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="R36" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="S36" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="T36" s="33" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="50"/>
-      <c r="B37" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="47"/>
-      <c r="T37" s="34"/>
-    </row>
-    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="50"/>
-      <c r="B38" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="40">
-        <f t="shared" ref="G38" si="27">SUM(D38:F38)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="37"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="44"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="R38" s="34"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="34"/>
-    </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="50"/>
-      <c r="B39" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="34"/>
-    </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="50"/>
-      <c r="B40" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="40">
-        <f t="shared" ref="G40" si="28">SUM(D40:F40)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="R40" s="34"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="34"/>
-    </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="50"/>
-      <c r="B41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45"/>
-      <c r="O41" s="45"/>
-      <c r="P41" s="45"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="35"/>
-    </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="50">
-        <v>7</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="38">
-        <v>84287</v>
-      </c>
-      <c r="E42" s="38">
-        <v>83840</v>
-      </c>
-      <c r="F42" s="38">
-        <v>84075</v>
-      </c>
-      <c r="G42" s="40">
-        <f t="shared" ref="G42" si="29">SUM(D42:F42)</f>
-        <v>252202</v>
-      </c>
-      <c r="H42" s="37">
-        <f>SUM(G42:G46)</f>
-        <v>252202</v>
-      </c>
-      <c r="I42" s="49">
-        <v>457</v>
-      </c>
-      <c r="J42" s="49">
-        <v>453</v>
-      </c>
-      <c r="K42" s="49">
-        <v>454</v>
-      </c>
-      <c r="L42" s="49"/>
-      <c r="M42" s="44">
-        <f t="shared" ref="M42:O42" si="30">(100*D42)/$T$3</f>
-        <v>93.652222222222221</v>
-      </c>
-      <c r="N42" s="44">
-        <f t="shared" si="30"/>
-        <v>93.155555555555551</v>
-      </c>
-      <c r="O42" s="44">
-        <f t="shared" si="30"/>
-        <v>93.416666666666671</v>
-      </c>
-      <c r="P42" s="44">
-        <f>(H42*100)/$S$3</f>
-        <v>93.408148148148143</v>
-      </c>
-      <c r="Q42" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="R42" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="S42" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T42" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="50"/>
-      <c r="B43" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="44"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-    </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="50"/>
-      <c r="B44" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="40">
-        <f t="shared" ref="G44" si="31">SUM(D44:F44)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="49"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-    </row>
-    <row r="45" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="50"/>
-      <c r="B45" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="49"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="34"/>
-    </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
-      <c r="B46" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" s="36"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="40">
-        <f t="shared" ref="G46" si="32">SUM(D46:F46)</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="49"/>
-      <c r="L46" s="49"/>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="R46" s="34"/>
-      <c r="S46" s="34"/>
-      <c r="T46" s="34"/>
-    </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="50"/>
-      <c r="B47" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="42"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="49"/>
-      <c r="L47" s="49"/>
-      <c r="M47" s="45"/>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="46"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-    </row>
-    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="31">
-        <f>SUM(D6:D47)</f>
-        <v>532573</v>
-      </c>
-      <c r="E48" s="31">
-        <f>SUM(E6:E47)</f>
-        <v>581884</v>
-      </c>
-      <c r="F48" s="31">
-        <f>SUM(F6:F47)</f>
-        <v>580790</v>
-      </c>
-      <c r="G48" s="31">
-        <f>SUM(G6:G46)</f>
-        <v>1695247</v>
-      </c>
-      <c r="H48" s="31">
-        <f>SUM(H6:H47)</f>
-        <v>1695247</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="30"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="J49" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L49" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="M49" s="26"/>
-      <c r="N49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O49" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q49" s="21"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="28"/>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="22"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="18"/>
-      <c r="O51" s="18"/>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="22"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="23"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="23"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="Q54" s="24"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="I64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J64" t="s">
-        <v>103</v>
-      </c>
-      <c r="K64" t="s">
-        <v>104</v>
-      </c>
-      <c r="M64" t="s">
-        <v>61</v>
-      </c>
-      <c r="O64" t="s">
-        <v>105</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="242">
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="T42:T47"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="Q44:Q45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="N42:N47"/>
-    <mergeCell ref="O42:O47"/>
-    <mergeCell ref="P42:P47"/>
-    <mergeCell ref="Q42:Q43"/>
-    <mergeCell ref="R42:R47"/>
-    <mergeCell ref="S42:S47"/>
-    <mergeCell ref="Q46:Q47"/>
-    <mergeCell ref="H42:H47"/>
-    <mergeCell ref="I42:I47"/>
-    <mergeCell ref="J42:J47"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="M42:M47"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="T36:T41"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="N36:N41"/>
-    <mergeCell ref="O36:O41"/>
-    <mergeCell ref="P36:P41"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="R36:R41"/>
-    <mergeCell ref="S36:S41"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="H36:H41"/>
-    <mergeCell ref="I36:I41"/>
-    <mergeCell ref="J36:J41"/>
-    <mergeCell ref="K36:K41"/>
-    <mergeCell ref="L36:L41"/>
-    <mergeCell ref="M36:M41"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="T30:T35"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="Q32:Q33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="N30:N35"/>
-    <mergeCell ref="O30:O35"/>
-    <mergeCell ref="P30:P35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="R30:R35"/>
-    <mergeCell ref="S30:S35"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="H30:H35"/>
-    <mergeCell ref="I30:I35"/>
-    <mergeCell ref="J30:J35"/>
-    <mergeCell ref="K30:K35"/>
-    <mergeCell ref="L30:L35"/>
-    <mergeCell ref="M30:M35"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="T24:T29"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="N24:N29"/>
-    <mergeCell ref="O24:O29"/>
-    <mergeCell ref="P24:P29"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="R24:R29"/>
-    <mergeCell ref="S24:S29"/>
-    <mergeCell ref="Q28:Q29"/>
-    <mergeCell ref="H24:H29"/>
-    <mergeCell ref="I24:I29"/>
-    <mergeCell ref="J24:J29"/>
-    <mergeCell ref="K24:K29"/>
-    <mergeCell ref="L24:L29"/>
-    <mergeCell ref="M24:M29"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="T18:T23"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="N18:N23"/>
-    <mergeCell ref="O18:O23"/>
-    <mergeCell ref="P18:P23"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R23"/>
-    <mergeCell ref="S18:S23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="H18:H23"/>
-    <mergeCell ref="I18:I23"/>
-    <mergeCell ref="J18:J23"/>
-    <mergeCell ref="K18:K23"/>
-    <mergeCell ref="L18:L23"/>
-    <mergeCell ref="M18:M23"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="R12:R17"/>
-    <mergeCell ref="S12:S17"/>
-    <mergeCell ref="T12:T17"/>
-    <mergeCell ref="I12:I17"/>
-    <mergeCell ref="J12:J17"/>
-    <mergeCell ref="K12:K17"/>
-    <mergeCell ref="L12:L17"/>
-    <mergeCell ref="M12:M17"/>
-    <mergeCell ref="N12:N17"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="O12:O17"/>
-    <mergeCell ref="P12:P17"/>
-    <mergeCell ref="Q12:Q13"/>
-    <mergeCell ref="J6:J11"/>
-    <mergeCell ref="K6:K11"/>
-    <mergeCell ref="L6:L11"/>
-    <mergeCell ref="M6:M11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="T6:T11"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="N6:N11"/>
-    <mergeCell ref="O6:O11"/>
-    <mergeCell ref="P6:P11"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R11"/>
-    <mergeCell ref="S6:S11"/>
-    <mergeCell ref="H6:H11"/>
-    <mergeCell ref="I6:I11"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:R3"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:T4"/>
-  </mergeCells>
-  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="94" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FC6C7D-DB58-47D8-B3A9-D523C89525DC}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:T64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="12" max="12" width="5.33203125" customWidth="1"/>
-    <col min="13" max="13" width="7.109375" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="15" width="7.44140625" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" customWidth="1"/>
-    <col min="18" max="20" width="20.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="68"/>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="86" t="s">
-        <v>171</v>
-      </c>
-      <c r="T1" s="87"/>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="8">
-        <v>270000</v>
-      </c>
-      <c r="T3" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="90" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="92" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="93"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="R4" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="64"/>
-      <c r="T4" s="65"/>
-    </row>
-    <row r="5" spans="1:20" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="89"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="66">
-        <v>1</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="67">
-        <v>85522</v>
-      </c>
-      <c r="E6" s="67">
-        <v>81122</v>
-      </c>
-      <c r="F6" s="67">
-        <v>79005</v>
-      </c>
-      <c r="G6" s="40">
-        <f>SUM(D6:F6)</f>
-        <v>245649</v>
-      </c>
-      <c r="H6" s="40">
-        <f>SUM(G6:G10)</f>
-        <v>245649</v>
-      </c>
-      <c r="I6" s="40">
-        <v>451</v>
-      </c>
-      <c r="J6" s="40">
-        <v>428</v>
-      </c>
-      <c r="K6" s="40">
-        <v>412</v>
-      </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="57">
-        <f>(100*D6)/$T$3</f>
-        <v>95.024444444444441</v>
-      </c>
-      <c r="N6" s="57">
-        <f t="shared" ref="N6:O6" si="0">(100*E6)/$T$3</f>
-        <v>90.135555555555555</v>
-      </c>
-      <c r="O6" s="57">
-        <f t="shared" si="0"/>
-        <v>87.783333333333331</v>
-      </c>
-      <c r="P6" s="57">
-        <f>(H6*100)/$S$3</f>
-        <v>90.981111111111105</v>
-      </c>
-      <c r="Q6" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="R6" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="T6" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="55"/>
-      <c r="B7" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55"/>
-      <c r="B8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="40">
-        <f t="shared" ref="G8" si="1">SUM(D8:F8)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="52"/>
-      <c r="Q8" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="55"/>
-      <c r="B9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55"/>
-      <c r="B10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="40">
-        <f t="shared" ref="G10" si="2">SUM(D10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-    </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
-      <c r="B11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <v>2</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="38">
-        <v>85120</v>
-      </c>
-      <c r="E12" s="38">
-        <v>84021</v>
-      </c>
-      <c r="F12" s="38">
-        <v>78132</v>
-      </c>
-      <c r="G12" s="40">
-        <f t="shared" ref="G12" si="3">SUM(D12:F12)</f>
-        <v>247273</v>
-      </c>
-      <c r="H12" s="36">
-        <f t="shared" ref="H12" si="4">SUM(G12:G16)</f>
-        <v>247273</v>
-      </c>
-      <c r="I12" s="36">
-        <v>454</v>
-      </c>
-      <c r="J12" s="36">
-        <v>451</v>
-      </c>
-      <c r="K12" s="36">
-        <v>419</v>
-      </c>
-      <c r="L12" s="36">
-        <v>12</v>
-      </c>
-      <c r="M12" s="51">
-        <f>(100*D12)/$T$3</f>
-        <v>94.577777777777783</v>
-      </c>
-      <c r="N12" s="51">
-        <f t="shared" ref="N12:O12" si="5">(100*E12)/$T$3</f>
-        <v>93.356666666666669</v>
-      </c>
-      <c r="O12" s="51">
-        <f t="shared" si="5"/>
-        <v>86.813333333333333</v>
-      </c>
-      <c r="P12" s="51">
-        <f>(H12*100)/$S$3</f>
-        <v>91.58259259259259</v>
-      </c>
-      <c r="Q12" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="R12" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S12" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T12" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="55"/>
-      <c r="B13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55"/>
-      <c r="B14" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="40">
-        <f t="shared" ref="G14" si="6">SUM(D14:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="55"/>
-      <c r="B15" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="40">
-        <f t="shared" ref="G16" si="7">SUM(D16:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-    </row>
-    <row r="17" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
-      <c r="B17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-    </row>
-    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <v>3</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="38">
-        <v>80001</v>
-      </c>
-      <c r="E18" s="38">
-        <v>76447</v>
-      </c>
-      <c r="F18" s="38">
-        <v>72520</v>
-      </c>
-      <c r="G18" s="40">
-        <f t="shared" ref="G18" si="8">SUM(D18:F18)</f>
-        <v>228968</v>
-      </c>
-      <c r="H18" s="36">
-        <f t="shared" ref="H18" si="9">SUM(G18:G22)</f>
-        <v>228968</v>
-      </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="51">
-        <f t="shared" ref="M18:O18" si="10">(100*D18)/$T$3</f>
-        <v>88.89</v>
-      </c>
-      <c r="N18" s="51">
-        <f t="shared" si="10"/>
-        <v>84.941111111111113</v>
-      </c>
-      <c r="O18" s="51">
-        <f t="shared" si="10"/>
-        <v>80.577777777777783</v>
-      </c>
-      <c r="P18" s="51">
-        <f t="shared" ref="P18" si="11">(H18*100)/$S$3</f>
-        <v>84.802962962962965</v>
-      </c>
-      <c r="Q18" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="R18" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S18" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="55"/>
-      <c r="B19" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-    </row>
-    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="40">
-        <f t="shared" ref="G20" si="12">SUM(D20:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-    </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="55"/>
-      <c r="B21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-    </row>
-    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="55"/>
-      <c r="B22" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="40">
-        <f t="shared" ref="G22" si="13">SUM(D22:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-    </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
-      <c r="B23" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-    </row>
-    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50">
-        <v>4</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="40">
-        <f t="shared" ref="G24" si="14">SUM(D24:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="37">
-        <f>SUM(G24:G28)</f>
-        <v>234211</v>
-      </c>
-      <c r="I24" s="49">
-        <v>382</v>
-      </c>
-      <c r="J24" s="49">
-        <v>426</v>
-      </c>
-      <c r="K24" s="49">
-        <v>405</v>
-      </c>
-      <c r="L24" s="49"/>
-      <c r="M24" s="44">
-        <f t="shared" ref="M24:O24" si="15">(100*D24)/$T$3</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="44">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="44">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="44">
-        <f t="shared" ref="P24" si="16">(H24*100)/$S$3</f>
-        <v>86.744814814814816</v>
-      </c>
-      <c r="Q24" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="R24" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="S24" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="T24" s="33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="50"/>
-      <c r="B25" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-    </row>
-    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50"/>
-      <c r="B26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="40">
-        <f t="shared" ref="G26" si="17">SUM(D26:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-    </row>
-    <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="50"/>
-      <c r="B27" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-    </row>
-    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="50"/>
-      <c r="B28" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="38">
-        <v>73535</v>
-      </c>
-      <c r="E28" s="38">
-        <v>82454</v>
-      </c>
-      <c r="F28" s="38">
-        <v>78222</v>
-      </c>
-      <c r="G28" s="40">
-        <f t="shared" ref="G28" si="18">SUM(D28:F28)</f>
-        <v>234211</v>
-      </c>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-    </row>
-    <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="50"/>
-      <c r="B29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-    </row>
-    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="50">
-        <v>5</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="40">
-        <f t="shared" ref="G30" si="19">SUM(D30:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="37">
-        <f>SUM(G30:G34)</f>
-        <v>262138</v>
-      </c>
-      <c r="I30" s="49">
-        <v>462</v>
-      </c>
-      <c r="J30" s="49">
-        <v>448</v>
-      </c>
-      <c r="K30" s="49">
-        <v>405</v>
-      </c>
-      <c r="L30" s="49"/>
-      <c r="M30" s="44">
-        <f t="shared" ref="M30:O30" si="20">(100*D30)/$T$3</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="44">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="44">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="44">
-        <f t="shared" ref="P30" si="21">(H30*100)/$S$3</f>
-        <v>97.08814814814815</v>
-      </c>
-      <c r="Q30" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="R30" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S30" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T30" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="50"/>
-      <c r="B31" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-    </row>
-    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="40">
-        <f t="shared" ref="G32" si="22">SUM(D32:F32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-    </row>
-    <row r="33" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="50"/>
-      <c r="B33" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-    </row>
-    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="50"/>
-      <c r="B34" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="38">
-        <v>92004</v>
-      </c>
-      <c r="E34" s="38">
-        <v>89394</v>
-      </c>
-      <c r="F34" s="38">
-        <v>80740</v>
-      </c>
-      <c r="G34" s="40">
-        <f t="shared" ref="G34" si="23">SUM(D34:F34)</f>
-        <v>262138</v>
-      </c>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="41" t="s">
-        <v>194</v>
-      </c>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-    </row>
-    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="50"/>
-      <c r="B35" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-    </row>
-    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="50">
-        <v>6</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="38">
-        <v>80603</v>
-      </c>
-      <c r="E36" s="38">
-        <v>29843</v>
-      </c>
-      <c r="F36" s="38"/>
-      <c r="G36" s="40">
-        <f t="shared" ref="G36" si="24">SUM(D36:F36)</f>
-        <v>110446</v>
-      </c>
-      <c r="H36" s="37">
-        <f>SUM(G36:G40)</f>
-        <v>110446</v>
-      </c>
-      <c r="I36" s="49">
-        <v>426</v>
-      </c>
-      <c r="J36" s="49">
-        <v>157</v>
-      </c>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="44">
-        <f t="shared" ref="M36:O36" si="25">(100*D36)/$T$3</f>
-        <v>89.558888888888887</v>
-      </c>
-      <c r="N36" s="44">
-        <f t="shared" si="25"/>
-        <v>33.158888888888889</v>
-      </c>
-      <c r="O36" s="44">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="P36" s="44">
-        <f t="shared" ref="P36" si="26">(H36*100)/$S$3</f>
-        <v>40.905925925925928</v>
-      </c>
-      <c r="Q36" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="R36" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S36" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="T36" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="50"/>
-      <c r="B37" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="47"/>
-      <c r="T37" s="34"/>
-    </row>
-    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="50"/>
-      <c r="B38" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="40">
-        <f t="shared" ref="G38" si="27">SUM(D38:F38)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="37"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="44"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="41">
-        <v>32</v>
-      </c>
-      <c r="R38" s="34"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="34"/>
-    </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="50"/>
-      <c r="B39" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="34"/>
-    </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="50"/>
-      <c r="B40" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="40">
-        <f t="shared" ref="G40" si="28">SUM(D40:F40)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="34"/>
-    </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="50"/>
-      <c r="B41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45"/>
-      <c r="O41" s="45"/>
-      <c r="P41" s="45"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="35"/>
-    </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="50">
-        <v>7</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="38">
-        <v>85073</v>
-      </c>
-      <c r="E42" s="38">
-        <v>23293</v>
-      </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="40">
-        <f t="shared" ref="G42" si="29">SUM(D42:F42)</f>
-        <v>108366</v>
-      </c>
-      <c r="H42" s="37">
-        <f>SUM(G42:G46)</f>
-        <v>108366</v>
-      </c>
-      <c r="I42" s="49">
-        <v>460</v>
-      </c>
-      <c r="J42" s="49">
-        <v>126</v>
-      </c>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="44">
-        <f t="shared" ref="M42:O42" si="30">(100*D42)/$T$3</f>
-        <v>94.525555555555556</v>
-      </c>
-      <c r="N42" s="44">
-        <f t="shared" si="30"/>
-        <v>25.88111111111111</v>
-      </c>
-      <c r="O42" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="44">
-        <f>(H42*100)/$S$3</f>
-        <v>40.135555555555555</v>
-      </c>
-      <c r="Q42" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="R42" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="S42" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="T42" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="50"/>
-      <c r="B43" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="44"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="34"/>
-    </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="50"/>
-      <c r="B44" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="40">
-        <f t="shared" ref="G44" si="31">SUM(D44:F44)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="49"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="41">
-        <v>37</v>
-      </c>
-      <c r="R44" s="34"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="34"/>
-    </row>
-    <row r="45" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="50"/>
-      <c r="B45" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="49"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="34"/>
-    </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
-      <c r="B46" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" s="36"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="40">
-        <f t="shared" ref="G46" si="32">SUM(D46:F46)</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="49"/>
-      <c r="L46" s="49"/>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="34"/>
-      <c r="S46" s="48"/>
-      <c r="T46" s="34"/>
-    </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="50"/>
-      <c r="B47" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="42"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="49"/>
-      <c r="L47" s="49"/>
-      <c r="M47" s="45"/>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="46"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="48"/>
-      <c r="T47" s="35"/>
-    </row>
-    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="31">
-        <f>SUM(D6:D47)</f>
-        <v>581858</v>
-      </c>
-      <c r="E48" s="31">
-        <f>SUM(E6:E47)</f>
-        <v>466574</v>
-      </c>
-      <c r="F48" s="31">
-        <f>SUM(F6:F47)</f>
-        <v>388619</v>
-      </c>
-      <c r="G48" s="31">
-        <f>SUM(G6:G46)</f>
-        <v>1437051</v>
-      </c>
-      <c r="H48" s="31">
-        <f>SUM(H6:H47)</f>
-        <v>1437051</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="30"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="J49" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L49" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="M49" s="26"/>
-      <c r="N49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O49" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q49" s="21"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="27">
-        <v>6</v>
-      </c>
-      <c r="M50" s="28"/>
-      <c r="N50" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="O50" s="18">
-        <v>6</v>
-      </c>
-      <c r="P50" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q50" s="22"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="27">
-        <v>7</v>
-      </c>
-      <c r="M51" s="28"/>
-      <c r="N51" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="O51" s="18">
-        <v>7</v>
-      </c>
-      <c r="P51" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="22"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="23"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="23"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="Q54" s="24"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="I64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J64" t="s">
-        <v>103</v>
-      </c>
-      <c r="K64" t="s">
-        <v>104</v>
-      </c>
-      <c r="M64" t="s">
-        <v>61</v>
-      </c>
-      <c r="O64" t="s">
-        <v>105</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="242">
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:R3"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="T6:T11"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="N6:N11"/>
-    <mergeCell ref="O6:O11"/>
-    <mergeCell ref="P6:P11"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R11"/>
-    <mergeCell ref="S6:S11"/>
-    <mergeCell ref="H6:H11"/>
-    <mergeCell ref="I6:I11"/>
-    <mergeCell ref="J6:J11"/>
-    <mergeCell ref="K6:K11"/>
-    <mergeCell ref="L6:L11"/>
-    <mergeCell ref="M6:M11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H17"/>
-    <mergeCell ref="R12:R17"/>
-    <mergeCell ref="S12:S17"/>
-    <mergeCell ref="T12:T17"/>
-    <mergeCell ref="I12:I17"/>
-    <mergeCell ref="J12:J17"/>
-    <mergeCell ref="K12:K17"/>
-    <mergeCell ref="L12:L17"/>
-    <mergeCell ref="M12:M17"/>
-    <mergeCell ref="N12:N17"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="O12:O17"/>
-    <mergeCell ref="P12:P17"/>
-    <mergeCell ref="Q12:Q13"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="T18:T23"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="N18:N23"/>
-    <mergeCell ref="O18:O23"/>
-    <mergeCell ref="P18:P23"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R23"/>
-    <mergeCell ref="S18:S23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="H18:H23"/>
-    <mergeCell ref="I18:I23"/>
-    <mergeCell ref="J18:J23"/>
-    <mergeCell ref="K18:K23"/>
-    <mergeCell ref="L18:L23"/>
-    <mergeCell ref="M18:M23"/>
-    <mergeCell ref="Q28:Q29"/>
-    <mergeCell ref="H24:H29"/>
-    <mergeCell ref="I24:I29"/>
-    <mergeCell ref="J24:J29"/>
-    <mergeCell ref="K24:K29"/>
-    <mergeCell ref="L24:L29"/>
-    <mergeCell ref="M24:M29"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="T24:T29"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="N24:N29"/>
-    <mergeCell ref="O24:O29"/>
-    <mergeCell ref="P24:P29"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="R24:R29"/>
-    <mergeCell ref="S24:S29"/>
-    <mergeCell ref="T30:T35"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="Q32:Q33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="N30:N35"/>
-    <mergeCell ref="O30:O35"/>
-    <mergeCell ref="P30:P35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="R30:R35"/>
-    <mergeCell ref="S30:S35"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="H30:H35"/>
-    <mergeCell ref="I30:I35"/>
-    <mergeCell ref="J30:J35"/>
-    <mergeCell ref="K30:K35"/>
-    <mergeCell ref="L30:L35"/>
-    <mergeCell ref="M30:M35"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="H36:H41"/>
-    <mergeCell ref="I36:I41"/>
-    <mergeCell ref="J36:J41"/>
-    <mergeCell ref="K36:K41"/>
-    <mergeCell ref="L36:L41"/>
-    <mergeCell ref="M36:M41"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="T36:T41"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="N36:N41"/>
-    <mergeCell ref="O36:O41"/>
-    <mergeCell ref="P36:P41"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="R36:R41"/>
-    <mergeCell ref="S36:S41"/>
-    <mergeCell ref="T42:T47"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="Q44:Q45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="N42:N47"/>
-    <mergeCell ref="O42:O47"/>
-    <mergeCell ref="P42:P47"/>
-    <mergeCell ref="Q42:Q43"/>
-    <mergeCell ref="R42:R47"/>
-    <mergeCell ref="S42:S47"/>
-    <mergeCell ref="Q46:Q47"/>
-    <mergeCell ref="H42:H47"/>
-    <mergeCell ref="I42:I47"/>
-    <mergeCell ref="J42:J47"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="M42:M47"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-  </mergeCells>
-  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="94" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67755413-81F5-43EB-9B97-9F8CBA426C42}">
   <dimension ref="A1:S53"/>
@@ -20918,1955 +16639,4 @@
   <pageSetup paperSize="8" scale="94" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58648EDD-1F25-4911-9B42-94BC0677E445}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:T64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="12" max="12" width="5.33203125" customWidth="1"/>
-    <col min="13" max="13" width="7.109375" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="15" width="7.44140625" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" customWidth="1"/>
-    <col min="18" max="20" width="20.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="68"/>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="86" t="s">
-        <v>118</v>
-      </c>
-      <c r="T1" s="87"/>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="74"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="8">
-        <v>270000</v>
-      </c>
-      <c r="T3" s="6">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="90" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="92" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="93"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="R4" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="64"/>
-      <c r="T4" s="65"/>
-    </row>
-    <row r="5" spans="1:20" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="89"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="66">
-        <v>1</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="67">
-        <v>87094</v>
-      </c>
-      <c r="E6" s="67">
-        <v>89118</v>
-      </c>
-      <c r="F6" s="67">
-        <v>86110</v>
-      </c>
-      <c r="G6" s="40">
-        <f>SUM(D6:F6)</f>
-        <v>262322</v>
-      </c>
-      <c r="H6" s="40">
-        <f>SUM(G6:G10)</f>
-        <v>262322</v>
-      </c>
-      <c r="I6" s="40">
-        <v>455</v>
-      </c>
-      <c r="J6" s="40">
-        <v>459</v>
-      </c>
-      <c r="K6" s="40">
-        <v>454</v>
-      </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="57">
-        <f>(100*D6)/$T$3</f>
-        <v>96.771111111111111</v>
-      </c>
-      <c r="N6" s="57">
-        <f t="shared" ref="N6:O6" si="0">(100*E6)/$T$3</f>
-        <v>99.02</v>
-      </c>
-      <c r="O6" s="57">
-        <f t="shared" si="0"/>
-        <v>95.677777777777777</v>
-      </c>
-      <c r="P6" s="57">
-        <f>(H6*100)/$S$3</f>
-        <v>97.15629629629629</v>
-      </c>
-      <c r="Q6" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="R6" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="S6" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="T6" s="33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="55"/>
-      <c r="B7" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55"/>
-      <c r="B8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="40">
-        <f t="shared" ref="G8" si="1">SUM(D8:F8)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="52"/>
-      <c r="Q8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="55"/>
-      <c r="B9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55"/>
-      <c r="B10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="40">
-        <f t="shared" ref="G10" si="2">SUM(D10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-    </row>
-    <row r="11" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
-      <c r="B11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54">
-        <v>2</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="38">
-        <v>84604</v>
-      </c>
-      <c r="E12" s="38">
-        <v>88270</v>
-      </c>
-      <c r="F12" s="38">
-        <v>86964</v>
-      </c>
-      <c r="G12" s="40">
-        <f t="shared" ref="G12" si="3">SUM(D12:F12)</f>
-        <v>259838</v>
-      </c>
-      <c r="H12" s="36">
-        <f t="shared" ref="H12" si="4">SUM(G12:G16)</f>
-        <v>259838</v>
-      </c>
-      <c r="I12" s="36">
-        <v>451</v>
-      </c>
-      <c r="J12" s="36">
-        <v>460</v>
-      </c>
-      <c r="K12" s="36">
-        <v>464</v>
-      </c>
-      <c r="L12" s="36">
-        <v>12</v>
-      </c>
-      <c r="M12" s="51">
-        <f>(100*D12)/$T$3</f>
-        <v>94.004444444444445</v>
-      </c>
-      <c r="N12" s="51">
-        <f t="shared" ref="N12:O12" si="5">(100*E12)/$T$3</f>
-        <v>98.077777777777783</v>
-      </c>
-      <c r="O12" s="51">
-        <f t="shared" si="5"/>
-        <v>96.626666666666665</v>
-      </c>
-      <c r="P12" s="51">
-        <f>(H12*100)/$S$3</f>
-        <v>96.236296296296302</v>
-      </c>
-      <c r="Q12" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="R12" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="S12" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="T12" s="33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="55"/>
-      <c r="B13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55"/>
-      <c r="B14" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="40">
-        <f t="shared" ref="G14" si="6">SUM(D14:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="55"/>
-      <c r="B15" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="40">
-        <f t="shared" ref="G16" si="7">SUM(D16:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-    </row>
-    <row r="17" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="56"/>
-      <c r="B17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-    </row>
-    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54">
-        <v>3</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="38">
-        <v>3102</v>
-      </c>
-      <c r="E18" s="38">
-        <v>70388</v>
-      </c>
-      <c r="F18" s="38">
-        <v>85774</v>
-      </c>
-      <c r="G18" s="40">
-        <f t="shared" ref="G18" si="8">SUM(D18:F18)</f>
-        <v>159264</v>
-      </c>
-      <c r="H18" s="36">
-        <f t="shared" ref="H18" si="9">SUM(G18:G22)</f>
-        <v>159264</v>
-      </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="51">
-        <f t="shared" ref="M18:O18" si="10">(100*D18)/$T$3</f>
-        <v>3.4466666666666668</v>
-      </c>
-      <c r="N18" s="51">
-        <f t="shared" si="10"/>
-        <v>78.208888888888893</v>
-      </c>
-      <c r="O18" s="51">
-        <f t="shared" si="10"/>
-        <v>95.304444444444442</v>
-      </c>
-      <c r="P18" s="51">
-        <f t="shared" ref="P18" si="11">(H18*100)/$S$3</f>
-        <v>58.986666666666665</v>
-      </c>
-      <c r="Q18" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="R18" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="S18" s="116" t="s">
-        <v>131</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="55"/>
-      <c r="B19" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-    </row>
-    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="40">
-        <f t="shared" ref="G20" si="12">SUM(D20:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-    </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="55"/>
-      <c r="B21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-    </row>
-    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="55"/>
-      <c r="B22" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="40">
-        <f t="shared" ref="G22" si="13">SUM(D22:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-    </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="56"/>
-      <c r="B23" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-    </row>
-    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50">
-        <v>4</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="38">
-        <v>87573</v>
-      </c>
-      <c r="E24" s="38">
-        <v>90039</v>
-      </c>
-      <c r="F24" s="38">
-        <v>89647</v>
-      </c>
-      <c r="G24" s="40">
-        <f t="shared" ref="G24" si="14">SUM(D24:F24)</f>
-        <v>267259</v>
-      </c>
-      <c r="H24" s="37">
-        <f>SUM(G24:G28)</f>
-        <v>267259</v>
-      </c>
-      <c r="I24" s="49">
-        <v>453</v>
-      </c>
-      <c r="J24" s="49">
-        <v>455</v>
-      </c>
-      <c r="K24" s="49">
-        <v>464</v>
-      </c>
-      <c r="L24" s="49"/>
-      <c r="M24" s="44">
-        <f t="shared" ref="M24:O24" si="15">(100*D24)/$T$3</f>
-        <v>97.303333333333327</v>
-      </c>
-      <c r="N24" s="44">
-        <f t="shared" si="15"/>
-        <v>100.04333333333334</v>
-      </c>
-      <c r="O24" s="44">
-        <f t="shared" si="15"/>
-        <v>99.607777777777784</v>
-      </c>
-      <c r="P24" s="44">
-        <f t="shared" ref="P24" si="16">(H24*100)/$S$3</f>
-        <v>98.984814814814811</v>
-      </c>
-      <c r="Q24" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="R24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="S24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="T24" s="33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="50"/>
-      <c r="B25" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-    </row>
-    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50"/>
-      <c r="B26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="40">
-        <f t="shared" ref="G26" si="17">SUM(D26:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-    </row>
-    <row r="27" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="50"/>
-      <c r="B27" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-    </row>
-    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="50"/>
-      <c r="B28" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="40">
-        <f t="shared" ref="G28" si="18">SUM(D28:F28)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-    </row>
-    <row r="29" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="50"/>
-      <c r="B29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-    </row>
-    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="50">
-        <v>5</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="40">
-        <f t="shared" ref="G30" si="19">SUM(D30:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="37">
-        <f>SUM(G30:G34)</f>
-        <v>274903</v>
-      </c>
-      <c r="I30" s="49">
-        <v>455</v>
-      </c>
-      <c r="J30" s="49">
-        <v>450</v>
-      </c>
-      <c r="K30" s="49">
-        <v>465</v>
-      </c>
-      <c r="L30" s="49"/>
-      <c r="M30" s="44">
-        <f t="shared" ref="M30:O30" si="20">(100*D30)/$T$3</f>
-        <v>0</v>
-      </c>
-      <c r="N30" s="44">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="44">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="44">
-        <f t="shared" ref="P30" si="21">(H30*100)/$S$3</f>
-        <v>101.81592592592592</v>
-      </c>
-      <c r="Q30" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="R30" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="S30" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="T30" s="33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="50"/>
-      <c r="B31" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-    </row>
-    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="40">
-        <f t="shared" ref="G32" si="22">SUM(D32:F32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-    </row>
-    <row r="33" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="50"/>
-      <c r="B33" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-    </row>
-    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="50"/>
-      <c r="B34" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="38">
-        <v>90557</v>
-      </c>
-      <c r="E34" s="38">
-        <v>91710</v>
-      </c>
-      <c r="F34" s="38">
-        <v>92636</v>
-      </c>
-      <c r="G34" s="40">
-        <f t="shared" ref="G34" si="23">SUM(D34:F34)</f>
-        <v>274903</v>
-      </c>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-    </row>
-    <row r="35" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="50"/>
-      <c r="B35" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-    </row>
-    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="50">
-        <v>6</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="38">
-        <v>81004</v>
-      </c>
-      <c r="E36" s="38">
-        <v>2426</v>
-      </c>
-      <c r="F36" s="38">
-        <v>46971</v>
-      </c>
-      <c r="G36" s="40">
-        <f t="shared" ref="G36" si="24">SUM(D36:F36)</f>
-        <v>130401</v>
-      </c>
-      <c r="H36" s="37">
-        <f>SUM(G36:G40)</f>
-        <v>130401</v>
-      </c>
-      <c r="I36" s="49">
-        <v>428</v>
-      </c>
-      <c r="J36" s="49">
-        <v>12</v>
-      </c>
-      <c r="K36" s="49">
-        <v>248</v>
-      </c>
-      <c r="L36" s="49"/>
-      <c r="M36" s="44">
-        <f t="shared" ref="M36:O36" si="25">(100*D36)/$T$3</f>
-        <v>90.004444444444445</v>
-      </c>
-      <c r="N36" s="44">
-        <f t="shared" si="25"/>
-        <v>2.6955555555555555</v>
-      </c>
-      <c r="O36" s="44">
-        <f t="shared" si="25"/>
-        <v>52.19</v>
-      </c>
-      <c r="P36" s="44">
-        <f t="shared" ref="P36" si="26">(H36*100)/$S$3</f>
-        <v>48.296666666666667</v>
-      </c>
-      <c r="Q36" s="41" t="s">
-        <v>126</v>
-      </c>
-      <c r="R36" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="S36" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="T36" s="33" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="50"/>
-      <c r="B37" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="47"/>
-      <c r="T37" s="34"/>
-    </row>
-    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="50"/>
-      <c r="B38" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="40">
-        <f t="shared" ref="G38" si="27">SUM(D38:F38)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="37"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="44"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="47"/>
-      <c r="T38" s="34"/>
-    </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="50"/>
-      <c r="B39" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="34"/>
-    </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="50"/>
-      <c r="B40" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="40">
-        <f t="shared" ref="G40" si="28">SUM(D40:F40)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="R40" s="34"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="34"/>
-    </row>
-    <row r="41" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="50"/>
-      <c r="B41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45"/>
-      <c r="O41" s="45"/>
-      <c r="P41" s="45"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="35"/>
-    </row>
-    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="50">
-        <v>7</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="38">
-        <v>84140</v>
-      </c>
-      <c r="E42" s="38">
-        <v>3833</v>
-      </c>
-      <c r="F42" s="38">
-        <v>56023</v>
-      </c>
-      <c r="G42" s="40">
-        <f t="shared" ref="G42" si="29">SUM(D42:F42)</f>
-        <v>143996</v>
-      </c>
-      <c r="H42" s="37">
-        <f>SUM(G42:G46)</f>
-        <v>143996</v>
-      </c>
-      <c r="I42" s="49">
-        <v>455</v>
-      </c>
-      <c r="J42" s="49">
-        <v>15</v>
-      </c>
-      <c r="K42" s="49">
-        <v>303</v>
-      </c>
-      <c r="L42" s="49"/>
-      <c r="M42" s="44">
-        <f t="shared" ref="M42:O42" si="30">(100*D42)/$T$3</f>
-        <v>93.488888888888894</v>
-      </c>
-      <c r="N42" s="44">
-        <f t="shared" si="30"/>
-        <v>4.2588888888888885</v>
-      </c>
-      <c r="O42" s="44">
-        <f t="shared" si="30"/>
-        <v>62.247777777777777</v>
-      </c>
-      <c r="P42" s="44">
-        <f>(H42*100)/$S$3</f>
-        <v>53.331851851851852</v>
-      </c>
-      <c r="Q42" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="R42" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="S42" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="T42" s="33" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="50"/>
-      <c r="B43" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="44"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="34"/>
-    </row>
-    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="50"/>
-      <c r="B44" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="40">
-        <f t="shared" ref="G44" si="31">SUM(D44:F44)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="49"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="34"/>
-    </row>
-    <row r="45" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="50"/>
-      <c r="B45" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="49"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="34"/>
-    </row>
-    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
-      <c r="B46" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" s="36"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="40">
-        <f t="shared" ref="G46" si="32">SUM(D46:F46)</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="49"/>
-      <c r="L46" s="49"/>
-      <c r="M46" s="45"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="45"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="R46" s="34"/>
-      <c r="S46" s="48"/>
-      <c r="T46" s="34"/>
-    </row>
-    <row r="47" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="50"/>
-      <c r="B47" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="42"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="49"/>
-      <c r="L47" s="49"/>
-      <c r="M47" s="45"/>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="46"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="48"/>
-      <c r="T47" s="35"/>
-    </row>
-    <row r="48" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="31">
-        <f>SUM(D6:D47)</f>
-        <v>518074</v>
-      </c>
-      <c r="E48" s="31">
-        <f>SUM(E6:E47)</f>
-        <v>435784</v>
-      </c>
-      <c r="F48" s="31">
-        <f>SUM(F6:F47)</f>
-        <v>544125</v>
-      </c>
-      <c r="G48" s="31">
-        <f>SUM(G6:G46)</f>
-        <v>1497983</v>
-      </c>
-      <c r="H48" s="31">
-        <f>SUM(H6:H47)</f>
-        <v>1497983</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="30"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="J49" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L49" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="M49" s="26"/>
-      <c r="N49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O49" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q49" s="21"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J50" s="18">
-        <v>3</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="L50" s="27">
-        <v>6</v>
-      </c>
-      <c r="M50" s="28"/>
-      <c r="N50" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="O50" s="18">
-        <v>6</v>
-      </c>
-      <c r="P50" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q50" s="22"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="27">
-        <v>7</v>
-      </c>
-      <c r="M51" s="28"/>
-      <c r="N51" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="O51" s="18">
-        <v>7</v>
-      </c>
-      <c r="P51" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q51" s="22"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="23"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="23"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="Q54" s="24"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="I64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J64" t="s">
-        <v>103</v>
-      </c>
-      <c r="K64" t="s">
-        <v>104</v>
-      </c>
-      <c r="M64" t="s">
-        <v>61</v>
-      </c>
-      <c r="O64" t="s">
-        <v>105</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="242">
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:R3"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="T6:T11"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="N6:N11"/>
-    <mergeCell ref="O6:O11"/>
-    <mergeCell ref="P6:P11"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R11"/>
-    <mergeCell ref="S6:S11"/>
-    <mergeCell ref="H6:H11"/>
-    <mergeCell ref="I6:I11"/>
-    <mergeCell ref="J6:J11"/>
-    <mergeCell ref="K6:K11"/>
-    <mergeCell ref="L6:L11"/>
-    <mergeCell ref="M6:M11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="R12:R17"/>
-    <mergeCell ref="S12:S17"/>
-    <mergeCell ref="T12:T17"/>
-    <mergeCell ref="I12:I17"/>
-    <mergeCell ref="J12:J17"/>
-    <mergeCell ref="K12:K17"/>
-    <mergeCell ref="L12:L17"/>
-    <mergeCell ref="M12:M17"/>
-    <mergeCell ref="N12:N17"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="O12:O17"/>
-    <mergeCell ref="P12:P17"/>
-    <mergeCell ref="Q12:Q13"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="T18:T23"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="N18:N23"/>
-    <mergeCell ref="O18:O23"/>
-    <mergeCell ref="P18:P23"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R23"/>
-    <mergeCell ref="S18:S23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="H18:H23"/>
-    <mergeCell ref="I18:I23"/>
-    <mergeCell ref="J18:J23"/>
-    <mergeCell ref="K18:K23"/>
-    <mergeCell ref="L18:L23"/>
-    <mergeCell ref="M18:M23"/>
-    <mergeCell ref="Q28:Q29"/>
-    <mergeCell ref="H24:H29"/>
-    <mergeCell ref="I24:I29"/>
-    <mergeCell ref="J24:J29"/>
-    <mergeCell ref="K24:K29"/>
-    <mergeCell ref="L24:L29"/>
-    <mergeCell ref="M24:M29"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="T24:T29"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="N24:N29"/>
-    <mergeCell ref="O24:O29"/>
-    <mergeCell ref="P24:P29"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="R24:R29"/>
-    <mergeCell ref="S24:S29"/>
-    <mergeCell ref="T30:T35"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="Q32:Q33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="N30:N35"/>
-    <mergeCell ref="O30:O35"/>
-    <mergeCell ref="P30:P35"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="R30:R35"/>
-    <mergeCell ref="S30:S35"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="H30:H35"/>
-    <mergeCell ref="I30:I35"/>
-    <mergeCell ref="J30:J35"/>
-    <mergeCell ref="K30:K35"/>
-    <mergeCell ref="L30:L35"/>
-    <mergeCell ref="M30:M35"/>
-    <mergeCell ref="Q40:Q41"/>
-    <mergeCell ref="H36:H41"/>
-    <mergeCell ref="I36:I41"/>
-    <mergeCell ref="J36:J41"/>
-    <mergeCell ref="K36:K41"/>
-    <mergeCell ref="L36:L41"/>
-    <mergeCell ref="M36:M41"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="T36:T41"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="Q38:Q39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="N36:N41"/>
-    <mergeCell ref="O36:O41"/>
-    <mergeCell ref="P36:P41"/>
-    <mergeCell ref="Q36:Q37"/>
-    <mergeCell ref="R36:R41"/>
-    <mergeCell ref="S36:S41"/>
-    <mergeCell ref="T42:T47"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="Q44:Q45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="N42:N47"/>
-    <mergeCell ref="O42:O47"/>
-    <mergeCell ref="P42:P47"/>
-    <mergeCell ref="Q42:Q43"/>
-    <mergeCell ref="R42:R47"/>
-    <mergeCell ref="S42:S47"/>
-    <mergeCell ref="Q46:Q47"/>
-    <mergeCell ref="H42:H47"/>
-    <mergeCell ref="I42:I47"/>
-    <mergeCell ref="J42:J47"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="M42:M47"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-  </mergeCells>
-  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.19685039370078741" bottom="3.937007874015748E-2" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="94" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>